--- a/WorkBot/main/data/order_archive/Peters Supply/Peters Supply_Triphammer_20260724.xlsx
+++ b/WorkBot/main/data/order_archive/Peters Supply/Peters Supply_Triphammer_20260724.xlsx
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
         <v>15.78</v>
       </c>
       <c r="E8" t="n">
-        <v>31.56</v>
+        <v>63.12</v>
       </c>
     </row>
     <row r="9">
@@ -554,13 +554,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
         <v>15.78</v>
       </c>
       <c r="E9" t="n">
-        <v>47.34</v>
+        <v>63.12</v>
       </c>
     </row>
   </sheetData>
